--- a/Flujo/input/datos_album.xlsx
+++ b/Flujo/input/datos_album.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Admin\Codigo-Gatito\Flujo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E90749-7A40-41DB-9000-AE596EE683BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7845E76-9689-4132-BE66-E777AA8916A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{6B60DF32-F346-4E42-983A-4F154DC0417C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Repetidas</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>Doradas</t>
+  </si>
+  <si>
+    <t>Diferentes</t>
   </si>
 </sst>
 </file>
@@ -416,13 +419,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF1430D-AAF4-45E4-8282-B315F5DA5728}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -432,8 +435,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -443,8 +449,11 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -454,8 +463,11 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -465,8 +477,11 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -476,8 +491,11 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -487,8 +505,11 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -498,8 +519,11 @@
       <c r="C7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -509,8 +533,11 @@
       <c r="C8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -520,8 +547,11 @@
       <c r="C9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -531,8 +561,11 @@
       <c r="C10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -542,8 +575,11 @@
       <c r="C11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -553,8 +589,11 @@
       <c r="C12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -563,6 +602,65 @@
       </c>
       <c r="C13">
         <v>1</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Flujo/input/datos_album.xlsx
+++ b/Flujo/input/datos_album.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Admin\Codigo-Gatito\Flujo\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7845E76-9689-4132-BE66-E777AA8916A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C534E61C-FFEC-43DB-A1AF-1371F02F7A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{6B60DF32-F346-4E42-983A-4F154DC0417C}"/>
   </bookViews>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF1430D-AAF4-45E4-8282-B315F5DA5728}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -663,6 +663,720 @@
         <v>4</v>
       </c>
     </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>4</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>4</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>4</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>3</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>4</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>3</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>4</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>6</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
